--- a/research/traditional_assets/database/data/bulgaria/bulgaria_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_healthcare_products.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.031</v>
+        <v>0.11</v>
       </c>
       <c r="G2">
-        <v>0.07841584158415842</v>
+        <v>-0.3165322580645161</v>
       </c>
       <c r="H2">
-        <v>0.07841584158415842</v>
+        <v>-0.3165322580645161</v>
       </c>
       <c r="I2">
-        <v>-0.2495049504950495</v>
+        <v>-0.1733870967741935</v>
       </c>
       <c r="J2">
-        <v>-0.2495049504950495</v>
+        <v>-0.1733870967741935</v>
       </c>
       <c r="K2">
-        <v>-1.34</v>
+        <v>-0.911</v>
       </c>
       <c r="L2">
-        <v>-0.2653465346534654</v>
+        <v>-0.1836693548387097</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.036</v>
+        <v>0.004</v>
       </c>
       <c r="V2">
-        <v>0.00216867469879518</v>
+        <v>0.0002366863905325444</v>
       </c>
       <c r="W2">
-        <v>-0.4253968253968254</v>
+        <v>-0.5146892655367232</v>
       </c>
       <c r="X2">
-        <v>0.08085275634836236</v>
+        <v>0.1455237553678279</v>
       </c>
       <c r="Y2">
-        <v>-0.5062495817451877</v>
+        <v>-0.6602130209045511</v>
       </c>
       <c r="Z2">
-        <v>0.826919927951531</v>
+        <v>1.009361009361009</v>
       </c>
       <c r="AA2">
-        <v>-0.2063206156869166</v>
+        <v>-0.175010175010175</v>
       </c>
       <c r="AB2">
-        <v>0.07319806059877842</v>
+        <v>0.1354236750626304</v>
       </c>
       <c r="AC2">
-        <v>-0.279518676285695</v>
+        <v>-0.3104338500728053</v>
       </c>
       <c r="AD2">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AG2">
-        <v>3.144</v>
+        <v>2.626</v>
       </c>
       <c r="AH2">
-        <v>0.1607684529828109</v>
+        <v>0.1346646185355863</v>
       </c>
       <c r="AI2">
-        <v>0.6334661354581673</v>
+        <v>0.387905604719764</v>
       </c>
       <c r="AJ2">
-        <v>0.1592382495948136</v>
+        <v>0.1344873501997337</v>
       </c>
       <c r="AK2">
-        <v>0.6308186195826646</v>
+        <v>0.3875442739079102</v>
       </c>
       <c r="AL2">
-        <v>0.132</v>
+        <v>0.114</v>
       </c>
       <c r="AM2">
-        <v>0.131</v>
+        <v>0.109</v>
       </c>
       <c r="AN2">
-        <v>-3.434125269978402</v>
+        <v>-5.754923413566739</v>
       </c>
       <c r="AO2">
-        <v>-9.545454545454545</v>
+        <v>-7.543859649122806</v>
       </c>
       <c r="AP2">
-        <v>-3.39524838012959</v>
+        <v>-5.74617067833698</v>
       </c>
       <c r="AQ2">
-        <v>-9.618320610687023</v>
+        <v>-7.889908256880734</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.031</v>
+        <v>0.11</v>
       </c>
       <c r="G3">
-        <v>0.07841584158415842</v>
+        <v>-0.3165322580645161</v>
       </c>
       <c r="H3">
-        <v>0.07841584158415842</v>
+        <v>-0.3165322580645161</v>
       </c>
       <c r="I3">
-        <v>-0.2495049504950495</v>
+        <v>-0.1733870967741935</v>
       </c>
       <c r="J3">
-        <v>-0.2495049504950495</v>
+        <v>-0.1733870967741935</v>
       </c>
       <c r="K3">
-        <v>-1.34</v>
+        <v>-0.911</v>
       </c>
       <c r="L3">
-        <v>-0.2653465346534654</v>
+        <v>-0.1836693548387097</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.036</v>
+        <v>0.004</v>
       </c>
       <c r="V3">
-        <v>0.00216867469879518</v>
+        <v>0.0002366863905325444</v>
       </c>
       <c r="W3">
-        <v>-0.4253968253968254</v>
+        <v>-0.5146892655367232</v>
       </c>
       <c r="X3">
-        <v>0.08085275634836236</v>
+        <v>0.1455237553678279</v>
       </c>
       <c r="Y3">
-        <v>-0.5062495817451877</v>
+        <v>-0.6602130209045511</v>
       </c>
       <c r="Z3">
-        <v>0.826919927951531</v>
+        <v>1.009361009361009</v>
       </c>
       <c r="AA3">
-        <v>-0.2063206156869166</v>
+        <v>-0.175010175010175</v>
       </c>
       <c r="AB3">
-        <v>0.07319806059877842</v>
+        <v>0.1354236750626304</v>
       </c>
       <c r="AC3">
-        <v>-0.279518676285695</v>
+        <v>-0.3104338500728053</v>
       </c>
       <c r="AD3">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AG3">
-        <v>3.144</v>
+        <v>2.626</v>
       </c>
       <c r="AH3">
-        <v>0.1607684529828109</v>
+        <v>0.1346646185355863</v>
       </c>
       <c r="AI3">
-        <v>0.6334661354581673</v>
+        <v>0.387905604719764</v>
       </c>
       <c r="AJ3">
-        <v>0.1592382495948136</v>
+        <v>0.1344873501997337</v>
       </c>
       <c r="AK3">
-        <v>0.6308186195826646</v>
+        <v>0.3875442739079102</v>
       </c>
       <c r="AL3">
-        <v>0.132</v>
+        <v>0.114</v>
       </c>
       <c r="AM3">
-        <v>0.131</v>
+        <v>0.109</v>
       </c>
       <c r="AN3">
-        <v>-3.434125269978402</v>
+        <v>-5.754923413566739</v>
       </c>
       <c r="AO3">
-        <v>-9.545454545454545</v>
+        <v>-7.543859649122806</v>
       </c>
       <c r="AP3">
-        <v>-3.39524838012959</v>
+        <v>-5.74617067833698</v>
       </c>
       <c r="AQ3">
-        <v>-9.618320610687023</v>
+        <v>-7.889908256880734</v>
       </c>
     </row>
   </sheetData>
